--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Proyecto San Joaquín</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Proyecto San Joaquín</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CORPORACION MONUCIPAL DE ISLA DE PASCUA</t>
+          <t>CORPORACION MUNICIPAL DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL CLUB DE LA REINA SOCIAL DEPO</t>
+          <t>CORPORACION MUNICIPAL CLUB DE LA REINA SOCIAL DEPORTIVO Y RECREACIONAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MUSEO HISTÓRICO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dirección de Telecomunicaciones e Informática de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERÍA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION DE INTELIGENCIA DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIRECCION DE BIENESTAR SOCIAL DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DIRECTORIO DE TRANSPORTE DE SANTIAGO</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dirección de Telecomunicaciones e Informática de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17258,12 +17258,12 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Dirección de Telecomunicaciones e Informática de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Dirección de Telecomunicaciones e Informática de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1578,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1643,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1960,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2025,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2090,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2155,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2220,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2285,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2350,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2415,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2480,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2610,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2675,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2740,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2805,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2870,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2935,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3061,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3187,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3252,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3317,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3443,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3508,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3634,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3699,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3764,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3951,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4016,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4081,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4146,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4455,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4520,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4585,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4711,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4776,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4902,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5028,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5215,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5280,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5406,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5471,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5536,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5662,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5971,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6036,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6101,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6227,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6292,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6601,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6666,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6853,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6918,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6983,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7048,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7174,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7239,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7304,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7369,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7495,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7560,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7747,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7812,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7877,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7942,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8007,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8072,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8198,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8385,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8450,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8515,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8580,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8767,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8832,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8897,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8962,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9027,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9092,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9157,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9344,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9470,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9535,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9722,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9787,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9913,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10039,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10104,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10169,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10234,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10360,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10547,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10612,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10677,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10864,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10929,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11055,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11120,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11246,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11372,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11498,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11685,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11872,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11937,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12002,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12067,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12132,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12319,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12384,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12449,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12514,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12640,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12827,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12953,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13140,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13205,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13270,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13335,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13522,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13587,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13652,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13839,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13904,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13969,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14034,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14160,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14286,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14351,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14538,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14847,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14912,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15038,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15103,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15168,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15233,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15298,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15363,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15428,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15493,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15558,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15745,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15871,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15936,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16001,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16066,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16253,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16318,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16383,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16509,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16696,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16761,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16826,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16952,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17017,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17082,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17147,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17212,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17277,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17342,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17407,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17472,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17598,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17663,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17789,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17915,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18041,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18106,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18171,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18297,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18362,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18427,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18492,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18557,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18683,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18748,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18813,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18878,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19004,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19191,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19256,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19321,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19386,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19451,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19516,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19581,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19707,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +19837,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +19902,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +19967,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2026.xlsx
@@ -16863,7 +16863,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
